--- a/output_data/charts/0500000US39129.xlsx
+++ b/output_data/charts/0500000US39129.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.3803577515833289</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.5177628543599733</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.53873431533006</c:v>
+                  <c:v>0.5403654711577799</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5496468986641708</c:v>
+                  <c:v>0.5511985165274493</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6099288416351426</c:v>
+                  <c:v>0.6134662510210546</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6073404708116426</c:v>
+                  <c:v>0.6173850386479759</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.6386949387045916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.337101028042413</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>3.798636386938022</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.602359519912711</c:v>
+                  <c:v>3.60527751261421</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.393176210329278</c:v>
+                  <c:v>3.40075874857522</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.586248271035046</c:v>
+                  <c:v>3.589110974044377</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.820842746292113</c:v>
+                  <c:v>3.820581684789729</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.997876379548892</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.081866623607298</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>1.524239162010219</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.604268957992362</c:v>
+                  <c:v>1.604050184099277</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.682974559686888</c:v>
+                  <c:v>1.679113999421582</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.91477660939557</c:v>
+                  <c:v>1.930418257289079</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.075762040402056</c:v>
+                  <c:v>2.105987161011398</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.339200102963416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1937671564669788</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2426479383469182</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2472040370976541</c:v>
+                  <c:v>0.2471703259239056</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2637624436314133</c:v>
+                  <c:v>0.2636906483387489</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2616361424500475</c:v>
+                  <c:v>0.2617233733975695</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2701109910617817</c:v>
+                  <c:v>0.270208306039565</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2702789665047138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.121337711035757</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.596008270535363</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.653709765411893</c:v>
+                  <c:v>1.653484249284058</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.778269378031141</c:v>
+                  <c:v>1.777785338799952</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.871448331028047</c:v>
+                  <c:v>1.87874039375198</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.887502864813541</c:v>
+                  <c:v>1.898008646665793</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.951478490298916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>93.88556972926422</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>92.32070538780951</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>92.35372340425532</c:v>
+                  <c:v>92.34965225692076</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>92.3321705096571</c:v>
+                  <c:v>92.32745274833705</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>91.75596180445615</c:v>
+                  <c:v>91.72654075049594</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>91.33844088661887</c:v>
+                  <c:v>91.28782916284554</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>90.80247112197947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.53873431533006</v>
+        <v>0.5403654711577799</v>
       </c>
       <c r="C12" s="2">
-        <v>3.602359519912711</v>
+        <v>3.60527751261421</v>
       </c>
       <c r="D12" s="2">
-        <v>1.604268957992362</v>
+        <v>1.604050184099277</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2472040370976541</v>
+        <v>0.2471703259239056</v>
       </c>
       <c r="F12" s="2">
-        <v>1.653709765411893</v>
+        <v>1.653484249284058</v>
       </c>
       <c r="G12" s="2">
-        <v>92.35372340425532</v>
+        <v>92.34965225692076</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.5496468986641708</v>
+        <v>0.5511985165274493</v>
       </c>
       <c r="C13" s="2">
-        <v>3.393176210329278</v>
+        <v>3.40075874857522</v>
       </c>
       <c r="D13" s="2">
-        <v>1.682974559686888</v>
+        <v>1.679113999421582</v>
       </c>
       <c r="E13" s="2">
-        <v>0.2637624436314133</v>
+        <v>0.2636906483387489</v>
       </c>
       <c r="F13" s="2">
-        <v>1.778269378031141</v>
+        <v>1.777785338799952</v>
       </c>
       <c r="G13" s="2">
-        <v>92.3321705096571</v>
+        <v>92.32745274833705</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.6099288416351426</v>
+        <v>0.6134662510210546</v>
       </c>
       <c r="C14" s="2">
-        <v>3.586248271035046</v>
+        <v>3.589110974044377</v>
       </c>
       <c r="D14" s="2">
-        <v>1.91477660939557</v>
+        <v>1.930418257289079</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2616361424500475</v>
+        <v>0.2617233733975695</v>
       </c>
       <c r="F14" s="2">
-        <v>1.871448331028047</v>
+        <v>1.87874039375198</v>
       </c>
       <c r="G14" s="2">
-        <v>91.75596180445615</v>
+        <v>91.72654075049594</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.6073404708116426</v>
+        <v>0.6173850386479759</v>
       </c>
       <c r="C15" s="2">
-        <v>3.820842746292113</v>
+        <v>3.820581684789729</v>
       </c>
       <c r="D15" s="2">
-        <v>2.075762040402056</v>
+        <v>2.105987161011398</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2701109910617817</v>
+        <v>0.270208306039565</v>
       </c>
       <c r="F15" s="2">
-        <v>1.887502864813541</v>
+        <v>1.898008646665793</v>
       </c>
       <c r="G15" s="2">
-        <v>91.33844088661887</v>
+        <v>91.28782916284554</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.6386949387045916</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3.997876379548892</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.339200102963416</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2702789665047138</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.951478490298916</v>
+      </c>
+      <c r="G16" s="2">
+        <v>90.80247112197947</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39129.xlsx
+++ b/output_data/charts/0500000US39129.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.3803577515833289</c:v>
+                  <c:v>0.3785432364549695</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.395023772923891</c:v>
+                  <c:v>0.3914349038392794</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4054414510536143</c:v>
+                  <c:v>0.401870654551274</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3992759795570698</c:v>
+                  <c:v>0.395705793629669</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.4073858526003916</c:v>
+                  <c:v>0.4020880361173815</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4386657542418978</c:v>
+                  <c:v>0.4334169752057414</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4503329681984943</c:v>
+                  <c:v>0.4448692327743505</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4760338589901157</c:v>
+                  <c:v>0.4745410460685833</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4957056059484673</c:v>
+                  <c:v>0.4976152349467087</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5177628543599733</c:v>
+                  <c:v>0.5217510306721179</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.5403654711577799</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>3.337101028042413</c:v>
+                  <c:v>3.336921420882669</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.331784220498338</c:v>
+                  <c:v>3.333452491599342</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.533386680892683</c:v>
+                  <c:v>3.53503920906165</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.573963657013061</c:v>
+                  <c:v>3.575547866205306</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.58358464278786</c:v>
+                  <c:v>3.579994356659142</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.481251425663701</c:v>
+                  <c:v>3.477864149221779</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.809573487733208</c:v>
+                  <c:v>3.800503953427752</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.770188163201718</c:v>
+                  <c:v>3.765154139244891</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.800409645604916</c:v>
+                  <c:v>3.808736677169964</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.798636386938022</c:v>
+                  <c:v>3.830165762868433</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>3.60527751261421</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.081866623607298</c:v>
+                  <c:v>1.080014352350197</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.151109998927537</c:v>
+                  <c:v>1.147494101665833</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.184315817551347</c:v>
+                  <c:v>1.178939132599534</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.320272572402044</c:v>
+                  <c:v>1.311329961848993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.327972064970107</c:v>
+                  <c:v>1.320894469525959</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.382674457370462</c:v>
+                  <c:v>1.365175735668287</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.371863752542903</c:v>
+                  <c:v>1.343296550525676</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.422908480326819</c:v>
+                  <c:v>1.375129892622099</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.468183617618203</c:v>
+                  <c:v>1.398143843518088</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.524239162010219</c:v>
+                  <c:v>1.450638931180184</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.604050184099277</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.1937671564669788</c:v>
+                  <c:v>0.1919626838894869</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2055553569513459</c:v>
+                  <c:v>0.205548008865375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2187249933315551</c:v>
+                  <c:v>0.220495403382115</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2324673480976718</c:v>
+                  <c:v>0.236003903823973</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2380826411300989</c:v>
+                  <c:v>0.2433690744920993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.231615518239722</c:v>
+                  <c:v>0.2403972696485286</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.238207014066385</c:v>
+                  <c:v>0.2502389434355722</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2406134778168222</c:v>
+                  <c:v>0.2528576376861794</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2426892029122704</c:v>
+                  <c:v>0.2582778036055581</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2426479383469182</c:v>
+                  <c:v>0.2583095266606223</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.2471703259239056</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.121337711035757</c:v>
+                  <c:v>1.119483315392896</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.154684874700604</c:v>
+                  <c:v>1.147494101665833</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.250111140748644</c:v>
+                  <c:v>1.234062983445063</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.286555934128336</c:v>
+                  <c:v>1.268742791234141</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.361479992240269</c:v>
+                  <c:v>1.342056997742664</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.419522380726781</c:v>
+                  <c:v>1.393251329203881</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.476187992280006</c:v>
+                  <c:v>1.449300547397689</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.509460091052294</c:v>
+                  <c:v>1.482507793557326</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.535310418423725</c:v>
+                  <c:v>1.499733112936274</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.596008270535363</c:v>
+                  <c:v>1.551567819080692</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.653484249284058</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>93.88556972926422</c:v>
+                  <c:v>93.89307499102978</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>93.76184177599829</c:v>
+                  <c:v>93.77457639236434</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>93.40801991642216</c:v>
+                  <c:v>93.42959261696036</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>93.18746450880182</c:v>
+                  <c:v>93.21266968325791</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>93.08149480627127</c:v>
+                  <c:v>93.11159706546276</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>93.04627046375742</c:v>
+                  <c:v>93.08989454105178</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>92.653834785179</c:v>
+                  <c:v>92.71179077243896</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>92.58079592861223</c:v>
+                  <c:v>92.64980949082093</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>92.45770150949242</c:v>
+                  <c:v>92.53749332782341</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>92.32070538780951</c:v>
+                  <c:v>92.38756692953795</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>92.34965225692076</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>0.3803577515833289</v>
+        <v>0.3785432364549695</v>
       </c>
       <c r="C2" s="2">
-        <v>3.337101028042413</v>
+        <v>3.336921420882669</v>
       </c>
       <c r="D2" s="2">
-        <v>1.081866623607298</v>
+        <v>1.080014352350197</v>
       </c>
       <c r="E2" s="2">
-        <v>0.1937671564669788</v>
+        <v>0.1919626838894869</v>
       </c>
       <c r="F2" s="2">
-        <v>1.121337711035757</v>
+        <v>1.119483315392896</v>
       </c>
       <c r="G2" s="2">
-        <v>93.88556972926422</v>
+        <v>93.89307499102978</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.395023772923891</v>
+        <v>0.3914349038392794</v>
       </c>
       <c r="C3" s="2">
-        <v>3.331784220498338</v>
+        <v>3.333452491599342</v>
       </c>
       <c r="D3" s="2">
-        <v>1.151109998927537</v>
+        <v>1.147494101665833</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2055553569513459</v>
+        <v>0.205548008865375</v>
       </c>
       <c r="F3" s="2">
-        <v>1.154684874700604</v>
+        <v>1.147494101665833</v>
       </c>
       <c r="G3" s="2">
-        <v>93.76184177599829</v>
+        <v>93.77457639236434</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.4054414510536143</v>
+        <v>0.401870654551274</v>
       </c>
       <c r="C4" s="2">
-        <v>3.533386680892683</v>
+        <v>3.53503920906165</v>
       </c>
       <c r="D4" s="2">
-        <v>1.184315817551347</v>
+        <v>1.178939132599534</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2187249933315551</v>
+        <v>0.220495403382115</v>
       </c>
       <c r="F4" s="2">
-        <v>1.250111140748644</v>
+        <v>1.234062983445063</v>
       </c>
       <c r="G4" s="2">
-        <v>93.40801991642216</v>
+        <v>93.42959261696036</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3992759795570698</v>
+        <v>0.395705793629669</v>
       </c>
       <c r="C5" s="2">
-        <v>3.573963657013061</v>
+        <v>3.575547866205306</v>
       </c>
       <c r="D5" s="2">
-        <v>1.320272572402044</v>
+        <v>1.311329961848993</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2324673480976718</v>
+        <v>0.236003903823973</v>
       </c>
       <c r="F5" s="2">
-        <v>1.286555934128336</v>
+        <v>1.268742791234141</v>
       </c>
       <c r="G5" s="2">
-        <v>93.18746450880182</v>
+        <v>93.21266968325791</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.4073858526003916</v>
+        <v>0.4020880361173815</v>
       </c>
       <c r="C6" s="2">
-        <v>3.58358464278786</v>
+        <v>3.579994356659142</v>
       </c>
       <c r="D6" s="2">
-        <v>1.327972064970107</v>
+        <v>1.320894469525959</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2380826411300989</v>
+        <v>0.2433690744920993</v>
       </c>
       <c r="F6" s="2">
-        <v>1.361479992240269</v>
+        <v>1.342056997742664</v>
       </c>
       <c r="G6" s="2">
-        <v>93.08149480627127</v>
+        <v>93.11159706546276</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.4386657542418978</v>
+        <v>0.4334169752057414</v>
       </c>
       <c r="C7" s="2">
-        <v>3.481251425663701</v>
+        <v>3.477864149221779</v>
       </c>
       <c r="D7" s="2">
-        <v>1.382674457370462</v>
+        <v>1.365175735668287</v>
       </c>
       <c r="E7" s="2">
-        <v>0.231615518239722</v>
+        <v>0.2403972696485286</v>
       </c>
       <c r="F7" s="2">
-        <v>1.419522380726781</v>
+        <v>1.393251329203881</v>
       </c>
       <c r="G7" s="2">
-        <v>93.04627046375742</v>
+        <v>93.08989454105178</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.4503329681984943</v>
+        <v>0.4448692327743505</v>
       </c>
       <c r="C8" s="2">
-        <v>3.809573487733208</v>
+        <v>3.800503953427752</v>
       </c>
       <c r="D8" s="2">
-        <v>1.371863752542903</v>
+        <v>1.343296550525676</v>
       </c>
       <c r="E8" s="2">
-        <v>0.238207014066385</v>
+        <v>0.2502389434355722</v>
       </c>
       <c r="F8" s="2">
-        <v>1.476187992280006</v>
+        <v>1.449300547397689</v>
       </c>
       <c r="G8" s="2">
-        <v>92.653834785179</v>
+        <v>92.71179077243896</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.4760338589901157</v>
+        <v>0.4745410460685833</v>
       </c>
       <c r="C9" s="2">
-        <v>3.770188163201718</v>
+        <v>3.765154139244891</v>
       </c>
       <c r="D9" s="2">
-        <v>1.422908480326819</v>
+        <v>1.375129892622099</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2406134778168222</v>
+        <v>0.2528576376861794</v>
       </c>
       <c r="F9" s="2">
-        <v>1.509460091052294</v>
+        <v>1.482507793557326</v>
       </c>
       <c r="G9" s="2">
-        <v>92.58079592861223</v>
+        <v>92.64980949082093</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.4957056059484673</v>
+        <v>0.4976152349467087</v>
       </c>
       <c r="C10" s="2">
-        <v>3.800409645604916</v>
+        <v>3.808736677169964</v>
       </c>
       <c r="D10" s="2">
-        <v>1.468183617618203</v>
+        <v>1.398143843518088</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2426892029122704</v>
+        <v>0.2582778036055581</v>
       </c>
       <c r="F10" s="2">
-        <v>1.535310418423725</v>
+        <v>1.499733112936274</v>
       </c>
       <c r="G10" s="2">
-        <v>92.45770150949242</v>
+        <v>92.53749332782341</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.5177628543599733</v>
+        <v>0.5217510306721179</v>
       </c>
       <c r="C11" s="2">
-        <v>3.798636386938022</v>
+        <v>3.830165762868433</v>
       </c>
       <c r="D11" s="2">
-        <v>1.524239162010219</v>
+        <v>1.450638931180184</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2426479383469182</v>
+        <v>0.2583095266606223</v>
       </c>
       <c r="F11" s="2">
-        <v>1.596008270535363</v>
+        <v>1.551567819080692</v>
       </c>
       <c r="G11" s="2">
-        <v>92.32070538780951</v>
+        <v>92.38756692953795</v>
       </c>
     </row>
     <row r="12" spans="1:7">
